--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484188_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484188_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.204000000000001</v>
+        <v>8.309799999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>4.073</v>
+        <v>3.3191</v>
       </c>
       <c r="F2" t="n">
-        <v>5.1309</v>
+        <v>4.9907</v>
       </c>
       <c r="G2" t="n">
         <v>3.0856</v>
@@ -610,13 +610,13 @@
         <v>2.9758</v>
       </c>
       <c r="S2" t="n">
-        <v>3.8686</v>
+        <v>2.9744</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3015</v>
+        <v>1.5476</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5671</v>
+        <v>1.4268</v>
       </c>
       <c r="V2" t="n">
         <v>0.266</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. BORRERO PERLAZA</t>
+          <t>P. SANTIAGO PAZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.8852</v>
+        <v>8.163600000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>5.901</v>
+        <v>4.0288</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9841</v>
+        <v>4.1348</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3852</v>
+        <v>5.9374</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7452</v>
+        <v>3.9669</v>
       </c>
       <c r="I3" t="n">
-        <v>0.64</v>
+        <v>1.9705</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1608</v>
+        <v>5.4854</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3977</v>
+        <v>4.3506</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7631</v>
+        <v>1.1347</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2244</v>
+        <v>0.452</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3474</v>
+        <v>-0.3837</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.123</v>
+        <v>0.8357</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1903</v>
+        <v>0.3968</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1903</v>
+        <v>2.3806</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5756</v>
+        <v>1.8294</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7402</v>
+        <v>0.5273</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8354</v>
+        <v>1.3021</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. SANTIAGO PAZ</t>
+          <t>B. BORRERO PERLAZA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.2212</v>
+        <v>7.0128</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9462</v>
+        <v>5.0848</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2751</v>
+        <v>1.928</v>
       </c>
       <c r="G4" t="n">
-        <v>5.9374</v>
+        <v>4.3852</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9669</v>
+        <v>3.7452</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9705</v>
+        <v>0.64</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4854</v>
+        <v>4.1608</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3506</v>
+        <v>3.3977</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1347</v>
+        <v>0.7631</v>
       </c>
       <c r="M4" t="n">
-        <v>0.452</v>
+        <v>0.2244</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3837</v>
+        <v>0.3474</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8357</v>
+        <v>-0.123</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3968</v>
+        <v>1.1903</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3806</v>
+        <v>1.1903</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8871</v>
+        <v>1.7033</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5554</v>
+        <v>0.924</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4424</v>
+        <v>0.7793</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.2317</v>
+        <v>5.0364</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5789</v>
+        <v>1.1311</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6527</v>
+        <v>3.9052</v>
       </c>
       <c r="G5" t="n">
         <v>2.2778</v>
@@ -844,13 +844,13 @@
         <v>2.7774</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2316</v>
+        <v>2.0363</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6099</v>
+        <v>1.1621</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6217</v>
+        <v>0.8742</v>
       </c>
       <c r="V5" t="n">
         <v>-0.0713</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6763</v>
+        <v>1.5472</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.8879</v>
+        <v>-2.2134</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5643</v>
+        <v>3.7606</v>
       </c>
       <c r="G6" t="n">
         <v>-1.8579</v>
@@ -922,13 +922,13 @@
         <v>2.3806</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1536</v>
+        <v>1.0245</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0566</v>
+        <v>0.6179</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2102</v>
+        <v>0.4066</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.023</v>
+        <v>0.5316</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.191</v>
+        <v>-0.7205</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1679</v>
+        <v>1.2521</v>
       </c>
       <c r="G7" t="n">
         <v>0.1079</v>
@@ -1000,13 +1000,13 @@
         <v>1.1903</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3293</v>
+        <v>0.2253</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5498</v>
+        <v>-0.0793</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2204</v>
+        <v>0.3046</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5102</v>
+        <v>-0.6505</v>
       </c>
       <c r="E8" t="n">
         <v>-0.5738</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0636</v>
+        <v>-0.0766</v>
       </c>
       <c r="G8" t="n">
         <v>0.2084</v>
@@ -1078,13 +1078,13 @@
         <v>0.5952</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1786</v>
+        <v>-0.3188</v>
       </c>
       <c r="T8" t="n">
         <v>-0.4988</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3202</v>
+        <v>0.1799</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1352</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3269</v>
+        <v>-1.2124</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0251</v>
+        <v>-1.7984</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6982</v>
+        <v>0.586</v>
       </c>
       <c r="G9" t="n">
         <v>-1.54</v>
@@ -1156,13 +1156,13 @@
         <v>2.7774</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5034</v>
+        <v>0.6179</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0001</v>
+        <v>0.2269</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5032</v>
+        <v>0.391</v>
       </c>
       <c r="V9" t="n">
         <v>-2.0757</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6185</v>
+        <v>-1.5281</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6963</v>
+        <v>-1.634</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0779</v>
+        <v>0.1059</v>
       </c>
       <c r="G10" t="n">
         <v>-1.8583</v>
@@ -1234,13 +1234,13 @@
         <v>0.5952</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3554</v>
+        <v>-0.265</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4364</v>
+        <v>-0.3741</v>
       </c>
       <c r="U10" t="n">
-        <v>0.081</v>
+        <v>0.1091</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X. ASSALIT GARCÍA</t>
+          <t>R. DIAZ SANCHEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0299</v>
+        <v>-2.2723</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1497</v>
+        <v>-1.4674</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1796</v>
+        <v>-0.8048</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0851</v>
+        <v>-2.1249</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.927</v>
+        <v>-1.0431</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1581</v>
+        <v>-1.0818</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5804</v>
+        <v>-1.3201</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6153999999999999</v>
+        <v>-0.6399</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0351</v>
+        <v>-0.6802</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6655</v>
+        <v>-0.8048</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5425</v>
+        <v>-0.4032</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.123</v>
+        <v>-0.4016</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5952</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5871</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.873</v>
+        <v>-0.1474</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5613</v>
+        <v>-0.1474</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3117</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4129</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. DIAZ SANCHEZ</t>
+          <t>X. ASSALIT GARCÍA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3743</v>
+        <v>-2.4777</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5694</v>
+        <v>-0.2981</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8048</v>
+        <v>-2.1796</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1249</v>
+        <v>-1.0851</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0431</v>
+        <v>-0.927</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0818</v>
+        <v>-0.1581</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.3201</v>
+        <v>0.5804</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6399</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6802</v>
+        <v>-0.0351</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8048</v>
+        <v>-1.6655</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4032</v>
+        <v>-1.5425</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4016</v>
+        <v>-0.123</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.5952</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.5871</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2494</v>
+        <v>0.4252</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2494</v>
+        <v>0.1135</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>0.3117</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-2.4129</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8283</v>
+        <v>-3.3298</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.9491</v>
+        <v>-2.4787</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8792</v>
+        <v>-0.8511</v>
       </c>
       <c r="G13" t="n">
         <v>-2.6746</v>
@@ -1468,13 +1468,13 @@
         <v>1.3887</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.344</v>
+        <v>0.1545</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5498</v>
+        <v>-0.0793</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2057</v>
+        <v>0.2338</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2065</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.5073</v>
+        <v>19.1306</v>
       </c>
       <c r="E14" t="n">
-        <v>1.756200000000001</v>
+        <v>2.3795</v>
       </c>
       <c r="F14" t="n">
-        <v>16.7511</v>
+        <v>16.7512</v>
       </c>
       <c r="G14" t="n">
-        <v>4.861499999999999</v>
+        <v>4.8615</v>
       </c>
       <c r="H14" t="n">
         <v>-0.4499000000000004</v>
@@ -1519,7 +1519,7 @@
         <v>5.3116</v>
       </c>
       <c r="J14" t="n">
-        <v>6.568599999999999</v>
+        <v>6.5686</v>
       </c>
       <c r="K14" t="n">
         <v>4.820400000000001</v>
@@ -1546,13 +1546,13 @@
         <v>19.8386</v>
       </c>
       <c r="S14" t="n">
-        <v>9.636200000000001</v>
+        <v>10.2596</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3168</v>
+        <v>3.940399999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>6.319</v>
+        <v>6.319100000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-6.9016</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7891</v>
+        <v>1.6472</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4205</v>
+        <v>1.1145</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3686</v>
+        <v>0.5327</v>
       </c>
       <c r="G15" t="n">
         <v>1.5438</v>
@@ -1624,13 +1624,13 @@
         <v>0.3968</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1514</v>
+        <v>-0.2934</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0056</v>
+        <v>-0.3117</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1458</v>
+        <v>0.0183</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3417</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2881</v>
+        <v>0.5942</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0536</v>
+        <v>0.3257</v>
       </c>
       <c r="G16" t="n">
         <v>-0.261</v>
@@ -1702,13 +1702,13 @@
         <v>0.9919</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2584</v>
+        <v>-0.6802</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8615</v>
+        <v>-0.5554</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3969</v>
+        <v>-0.1248</v>
       </c>
       <c r="V16" t="n">
         <v>0.8692</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. FABREGAS CANALS</t>
+          <t>P. MAJORAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0625</v>
+        <v>-1.4489</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.2466</v>
+        <v>-1.466</v>
       </c>
       <c r="F17" t="n">
-        <v>1.184</v>
+        <v>0.0171</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9722</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.826</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7982</v>
+        <v>0.25</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6243</v>
+        <v>1.538</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0162</v>
+        <v>0.3682</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.6405</v>
+        <v>1.1698</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3479</v>
+        <v>-0.7593</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1902</v>
+        <v>0.1605</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8421999999999999</v>
+        <v>-0.9198</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.7855</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9758</v>
+        <v>-1.9838</v>
       </c>
       <c r="R17" t="n">
         <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2227</v>
+        <v>-1.434</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1189</v>
+        <v>-1.0202</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3416</v>
+        <v>-0.4139</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. MAJORAL DE LOS RIOS</t>
+          <t>G. FABREGAS CANALS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0474</v>
+        <v>-1.5191</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5681</v>
+        <v>-2.4506</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4794</v>
+        <v>0.9315</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7786999999999999</v>
+        <v>-0.9722</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.826</v>
       </c>
       <c r="I18" t="n">
-        <v>0.25</v>
+        <v>-1.7982</v>
       </c>
       <c r="J18" t="n">
-        <v>1.538</v>
+        <v>-0.6243</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3682</v>
+        <v>2.0162</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1698</v>
+        <v>-2.6405</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7593</v>
+        <v>-0.3479</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1605</v>
+        <v>-1.1902</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9198</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7935</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R18" t="n">
         <v>1.1903</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.0326</v>
+        <v>-0.2339</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1222</v>
+        <v>-0.323</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9104</v>
+        <v>0.0891</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. GUTIÉRREZ MONREAL</t>
+          <t>O. BESORA TOMAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2117</v>
+        <v>-1.8106</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3343</v>
+        <v>-1.8508</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1226</v>
+        <v>0.0402</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6304</v>
+        <v>0.4353</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1367</v>
+        <v>2.5497</v>
       </c>
       <c r="I19" t="n">
-        <v>0.767</v>
+        <v>-2.1144</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3159</v>
+        <v>1.3897</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3911</v>
+        <v>2.1828</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0752</v>
+        <v>-0.793</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6856</v>
+        <v>-0.9544</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5278</v>
+        <v>0.367</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8421999999999999</v>
+        <v>-1.3214</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.1822</v>
+        <v>-2.7774</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9758</v>
+        <v>-3.9677</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3343</v>
+        <v>-1.2782</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6744</v>
+        <v>-1.0825</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6599</v>
+        <v>-0.1957</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6745</v>
+        <v>1.8097</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.8097</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. BESORA TOMAS</t>
+          <t>G. GUTIÉRREZ MONREAL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.353</v>
+        <v>-1.8155</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9528</v>
+        <v>-2.1302</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4002</v>
+        <v>0.3147</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4353</v>
+        <v>0.6304</v>
       </c>
       <c r="H20" t="n">
-        <v>2.5497</v>
+        <v>-0.1367</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.1144</v>
+        <v>0.767</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3897</v>
+        <v>1.3159</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1828</v>
+        <v>1.3911</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.793</v>
+        <v>-0.0752</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9544</v>
+        <v>-0.6856</v>
       </c>
       <c r="N20" t="n">
-        <v>0.367</v>
+        <v>-1.5278</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3214</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.7774</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.9677</v>
+        <v>-2.9758</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.8206</v>
+        <v>-0.9381</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1846</v>
+        <v>-0.4704</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6361</v>
+        <v>-0.4677</v>
       </c>
       <c r="V20" t="n">
-        <v>1.8097</v>
+        <v>0.6745</v>
       </c>
       <c r="W20" t="n">
-        <v>1.8097</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6223</v>
+        <v>-2.6546</v>
       </c>
       <c r="E21" t="n">
         <v>-1.8244</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.8302</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3496</v>
@@ -2092,13 +2092,13 @@
         <v>0.7935</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2969</v>
+        <v>-1.3292</v>
       </c>
       <c r="T21" t="n">
         <v>-0.9352</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3617</v>
+        <v>-0.394</v>
       </c>
       <c r="V21" t="n">
         <v>1.2065</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.905</v>
+        <v>-2.9934</v>
       </c>
       <c r="E22" t="n">
         <v>-1.7697</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1353</v>
+        <v>-1.2237</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0775</v>
@@ -2170,13 +2170,13 @@
         <v>0.7935</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.034</v>
+        <v>-1.1224</v>
       </c>
       <c r="T22" t="n">
         <v>-1.0485</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0146</v>
+        <v>-0.0738</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6032</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.4362</v>
+        <v>-7.472</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.764</v>
+        <v>-6.9681</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6722</v>
+        <v>-0.5039</v>
       </c>
       <c r="G23" t="n">
         <v>-6.5893</v>
@@ -2248,13 +2248,13 @@
         <v>1.5871</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9307</v>
+        <v>-0.9664</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3683</v>
+        <v>-0.5724</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5624</v>
+        <v>-0.394</v>
       </c>
       <c r="V23" t="n">
         <v>1.4724</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-18.5073</v>
+        <v>-17.147</v>
       </c>
       <c r="E24" t="n">
-        <v>-16.7513</v>
+        <v>-16.7511</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7562</v>
+        <v>-0.3959000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-4.8614</v>
@@ -2326,13 +2326,13 @@
         <v>8.927199999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-9.636199999999999</v>
+        <v>-8.275799999999998</v>
       </c>
       <c r="T24" t="n">
-        <v>-6.319199999999999</v>
+        <v>-6.3193</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.317</v>
+        <v>-1.9565</v>
       </c>
       <c r="V24" t="n">
         <v>6.9015</v>
